--- a/game-data/workbooks/development-data.xlsx
+++ b/game-data/workbooks/development-data.xlsx
@@ -1,57 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\ostatnia-szansa-game\game-data\workbooks\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9F13EE3-B4B9-4655-9D10-C97A5FB32B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="947" firstSheet="9" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="20"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" r:id="rId1"/>
-    <sheet name="IMPORT_ORDER" sheetId="2" r:id="rId2"/>
-    <sheet name="ENUMS" sheetId="3" r:id="rId3"/>
-    <sheet name="achievements" sheetId="4" r:id="rId4"/>
-    <sheet name="affix_templates" sheetId="5" r:id="rId5"/>
-    <sheet name="announcements" sheetId="6" r:id="rId6"/>
-    <sheet name="chest_definitions" sheetId="7" r:id="rId7"/>
-    <sheet name="consumable_definitions" sheetId="8" r:id="rId8"/>
-    <sheet name="mail_templates" sheetId="9" r:id="rId9"/>
-    <sheet name="materials" sheetId="10" r:id="rId10"/>
-    <sheet name="monster_families" sheetId="11" r:id="rId11"/>
-    <sheet name="npc_definitions" sheetId="12" r:id="rId12"/>
-    <sheet name="outfit_definitions" sheetId="13" r:id="rId13"/>
-    <sheet name="seasons" sheetId="14" r:id="rId14"/>
-    <sheet name="set_templates" sheetId="15" r:id="rId15"/>
-    <sheet name="spells" sheetId="16" r:id="rId16"/>
-    <sheet name="unique_templates" sheetId="17" r:id="rId17"/>
-    <sheet name="addon_definitions" sheetId="18" r:id="rId18"/>
-    <sheet name="chest_reward_definitions" sheetId="19" r:id="rId19"/>
-    <sheet name="item_bases" sheetId="20" r:id="rId20"/>
-    <sheet name="monsters" sheetId="21" r:id="rId21"/>
-    <sheet name="recipes" sheetId="22" r:id="rId22"/>
-    <sheet name="set_bonuses" sheetId="23" r:id="rId23"/>
-    <sheet name="bosses" sheetId="24" r:id="rId24"/>
-    <sheet name="loot_tables" sheetId="25" r:id="rId25"/>
-    <sheet name="monster_abilities" sheetId="26" r:id="rId26"/>
-    <sheet name="other_loot_tables" sheetId="27" r:id="rId27"/>
-    <sheet name="recipe_materials" sheetId="28" r:id="rId28"/>
-    <sheet name="daily_boss_definitions" sheetId="29" r:id="rId29"/>
-    <sheet name="monster_ability_weights" sheetId="30" r:id="rId30"/>
-    <sheet name="monster_tasks" sheetId="31" r:id="rId31"/>
-    <sheet name="daily_boss_pools" sheetId="32" r:id="rId32"/>
+    <sheet sheetId="1" name="README" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="IMPORT_ORDER" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="ENUMS" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="achievements" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="affix_templates" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="announcements" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="chest_definitions" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="consumable_definitions" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="mail_templates" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="materials" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="monster_families" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="npc_definitions" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="outfit_definitions" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="seasons" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="set_templates" state="visible" r:id="rId18"/>
+    <sheet sheetId="16" name="spells" state="visible" r:id="rId19"/>
+    <sheet sheetId="17" name="unique_templates" state="visible" r:id="rId20"/>
+    <sheet sheetId="18" name="addon_definitions" state="visible" r:id="rId21"/>
+    <sheet sheetId="19" name="chest_reward_definitions" state="visible" r:id="rId22"/>
+    <sheet sheetId="20" name="item_bases" state="visible" r:id="rId23"/>
+    <sheet sheetId="21" name="monsters" state="visible" r:id="rId24"/>
+    <sheet sheetId="22" name="recipes" state="visible" r:id="rId25"/>
+    <sheet sheetId="23" name="set_bonuses" state="visible" r:id="rId26"/>
+    <sheet sheetId="24" name="bosses" state="visible" r:id="rId27"/>
+    <sheet sheetId="25" name="loot_tables" state="visible" r:id="rId28"/>
+    <sheet sheetId="26" name="monster_abilities" state="visible" r:id="rId29"/>
+    <sheet sheetId="27" name="other_loot_tables" state="visible" r:id="rId30"/>
+    <sheet sheetId="28" name="recipe_materials" state="visible" r:id="rId31"/>
+    <sheet sheetId="29" name="daily_boss_definitions" state="visible" r:id="rId32"/>
+    <sheet sheetId="30" name="monster_ability_weights" state="visible" r:id="rId33"/>
+    <sheet sheetId="31" name="monster_tasks" state="visible" r:id="rId34"/>
+    <sheet sheetId="32" name="daily_boss_pools" state="visible" r:id="rId35"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2059" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2060" uniqueCount="849">
   <si>
     <t>GAME DATA AUTHORING WORKBOOK</t>
   </si>
@@ -2324,9 +2318,15 @@
     <t>loot_level_modifier</t>
   </si>
   <si>
+    <t>energy cost</t>
+  </si>
+  <si>
     <t>power_score</t>
   </si>
   <si>
+    <t>experience_reward</t>
+  </si>
+  <si>
     <t>Dev Monster 1</t>
   </si>
   <si>
@@ -2592,22 +2592,19 @@
   </si>
   <si>
     <t>daily_boss_definition_code</t>
-  </si>
-  <si>
-    <t>energy cost</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2637,7 +2634,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2933,11 +2930,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2945,7 +2942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -2953,7 +2950,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2961,7 +2958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2969,7 +2966,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2977,7 +2974,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2985,7 +2982,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2993,7 +2990,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -3001,7 +2998,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3009,7 +3006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -3023,11 +3020,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>170</v>
       </c>
@@ -3068,7 +3065,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>424</v>
       </c>
@@ -3109,7 +3106,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>431</v>
       </c>
@@ -3150,7 +3147,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>435</v>
       </c>
@@ -3191,7 +3188,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>439</v>
       </c>
@@ -3229,7 +3226,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>443</v>
       </c>
@@ -3267,7 +3264,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>446</v>
       </c>
@@ -3305,7 +3302,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>449</v>
       </c>
@@ -3343,7 +3340,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>452</v>
       </c>
@@ -3381,7 +3378,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>455</v>
       </c>
@@ -3419,7 +3416,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>458</v>
       </c>
@@ -3463,11 +3460,11 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>170</v>
       </c>
@@ -3478,7 +3475,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>461</v>
       </c>
@@ -3489,7 +3486,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>464</v>
       </c>
@@ -3500,7 +3497,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>466</v>
       </c>
@@ -3511,7 +3508,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>468</v>
       </c>
@@ -3522,7 +3519,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>470</v>
       </c>
@@ -3533,7 +3530,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>472</v>
       </c>
@@ -3544,7 +3541,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>474</v>
       </c>
@@ -3555,7 +3552,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>476</v>
       </c>
@@ -3566,7 +3563,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>478</v>
       </c>
@@ -3577,7 +3574,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>480</v>
       </c>
@@ -3594,11 +3591,11 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>170</v>
       </c>
@@ -3624,7 +3621,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>484</v>
       </c>
@@ -3650,7 +3647,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>488</v>
       </c>
@@ -3676,7 +3673,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>491</v>
       </c>
@@ -3702,7 +3699,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>494</v>
       </c>
@@ -3728,7 +3725,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>497</v>
       </c>
@@ -3754,7 +3751,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>500</v>
       </c>
@@ -3780,7 +3777,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>503</v>
       </c>
@@ -3806,7 +3803,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>506</v>
       </c>
@@ -3832,7 +3829,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>509</v>
       </c>
@@ -3858,7 +3855,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>512</v>
       </c>
@@ -3890,11 +3887,11 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>170</v>
       </c>
@@ -3914,7 +3911,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>516</v>
       </c>
@@ -3934,7 +3931,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>521</v>
       </c>
@@ -3954,7 +3951,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>524</v>
       </c>
@@ -3974,7 +3971,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>527</v>
       </c>
@@ -3994,7 +3991,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>530</v>
       </c>
@@ -4014,7 +4011,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>533</v>
       </c>
@@ -4034,7 +4031,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>536</v>
       </c>
@@ -4054,7 +4051,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>539</v>
       </c>
@@ -4074,7 +4071,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>542</v>
       </c>
@@ -4094,7 +4091,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>545</v>
       </c>
@@ -4120,11 +4117,11 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>548</v>
       </c>
@@ -4144,7 +4141,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4164,7 +4161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4184,7 +4181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4204,7 +4201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4224,7 +4221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4244,7 +4241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4264,7 +4261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4284,7 +4281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4304,7 +4301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4324,7 +4321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4350,11 +4347,11 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>170</v>
       </c>
@@ -4368,7 +4365,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>582</v>
       </c>
@@ -4382,7 +4379,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>585</v>
       </c>
@@ -4396,7 +4393,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>587</v>
       </c>
@@ -4410,7 +4407,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>589</v>
       </c>
@@ -4424,7 +4421,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>591</v>
       </c>
@@ -4438,7 +4435,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>593</v>
       </c>
@@ -4452,7 +4449,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>595</v>
       </c>
@@ -4466,7 +4463,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>597</v>
       </c>
@@ -4480,7 +4477,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>599</v>
       </c>
@@ -4494,7 +4491,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>601</v>
       </c>
@@ -4514,11 +4511,11 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>170</v>
       </c>
@@ -4556,7 +4553,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>610</v>
       </c>
@@ -4594,7 +4591,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>614</v>
       </c>
@@ -4632,7 +4629,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>617</v>
       </c>
@@ -4670,7 +4667,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>620</v>
       </c>
@@ -4708,7 +4705,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>623</v>
       </c>
@@ -4746,7 +4743,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>626</v>
       </c>
@@ -4784,7 +4781,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>629</v>
       </c>
@@ -4822,7 +4819,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>632</v>
       </c>
@@ -4860,7 +4857,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>635</v>
       </c>
@@ -4898,7 +4895,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>638</v>
       </c>
@@ -4942,11 +4939,11 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>170</v>
       </c>
@@ -4993,7 +4990,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>653</v>
       </c>
@@ -5040,7 +5037,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>656</v>
       </c>
@@ -5087,7 +5084,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>658</v>
       </c>
@@ -5134,7 +5131,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>660</v>
       </c>
@@ -5181,7 +5178,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>662</v>
       </c>
@@ -5228,7 +5225,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>664</v>
       </c>
@@ -5275,7 +5272,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>666</v>
       </c>
@@ -5322,7 +5319,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>668</v>
       </c>
@@ -5369,7 +5366,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>670</v>
       </c>
@@ -5416,7 +5413,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>672</v>
       </c>
@@ -5469,11 +5466,11 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>674</v>
       </c>
@@ -5490,7 +5487,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>520</v>
       </c>
@@ -5507,7 +5504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>523</v>
       </c>
@@ -5524,7 +5521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>526</v>
       </c>
@@ -5541,7 +5538,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>529</v>
       </c>
@@ -5558,7 +5555,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>532</v>
       </c>
@@ -5575,7 +5572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>535</v>
       </c>
@@ -5592,7 +5589,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>538</v>
       </c>
@@ -5609,7 +5606,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>541</v>
       </c>
@@ -5626,7 +5623,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>544</v>
       </c>
@@ -5643,7 +5640,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>547</v>
       </c>
@@ -5666,11 +5663,11 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>696</v>
       </c>
@@ -5693,7 +5690,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>171</v>
       </c>
@@ -5716,7 +5713,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>171</v>
       </c>
@@ -5739,7 +5736,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>171</v>
       </c>
@@ -5762,7 +5759,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>171</v>
       </c>
@@ -5785,7 +5782,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>171</v>
       </c>
@@ -5808,7 +5805,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>173</v>
       </c>
@@ -5831,7 +5828,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>173</v>
       </c>
@@ -5854,7 +5851,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>173</v>
       </c>
@@ -5877,7 +5874,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>173</v>
       </c>
@@ -5900,7 +5897,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>173</v>
       </c>
@@ -5929,11 +5926,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -5950,7 +5947,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5964,7 +5961,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5978,7 +5975,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5992,7 +5989,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -6006,7 +6003,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -6020,7 +6017,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -6034,7 +6031,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -6048,7 +6045,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -6062,7 +6059,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -6076,7 +6073,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -6090,7 +6087,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -6104,7 +6101,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -6118,7 +6115,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6132,7 +6129,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6146,7 +6143,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6163,7 +6160,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6180,7 +6177,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6197,7 +6194,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6214,7 +6211,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6231,7 +6228,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6248,7 +6245,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -6265,7 +6262,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -6282,7 +6279,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -6299,7 +6296,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -6316,7 +6313,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -6333,7 +6330,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -6350,7 +6347,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -6367,7 +6364,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -6384,7 +6381,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -6407,11 +6404,11 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:V11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>702</v>
       </c>
@@ -6479,7 +6476,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>718</v>
       </c>
@@ -6541,7 +6538,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>723</v>
       </c>
@@ -6600,7 +6597,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>726</v>
       </c>
@@ -6659,7 +6656,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>729</v>
       </c>
@@ -6718,7 +6715,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>732</v>
       </c>
@@ -6777,7 +6774,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>735</v>
       </c>
@@ -6836,7 +6833,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>738</v>
       </c>
@@ -6895,7 +6892,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>741</v>
       </c>
@@ -6954,7 +6951,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>744</v>
       </c>
@@ -7016,7 +7013,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>747</v>
       </c>
@@ -7081,14 +7078,14 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:R11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:S11"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
-    <col min="18" max="18" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>750</v>
       </c>
@@ -7135,27 +7132,30 @@
         <v>756</v>
       </c>
       <c r="P1" t="s">
-        <v>847</v>
+        <v>757</v>
       </c>
       <c r="Q1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="R1" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S1" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>463</v>
       </c>
       <c r="B2" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C2" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D2" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="E2" t="s">
         <v>126</v>
@@ -7197,21 +7197,24 @@
         <v>100</v>
       </c>
       <c r="R2" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+        <v>763</v>
+      </c>
+      <c r="S2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>465</v>
       </c>
       <c r="B3" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C3" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D3" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="E3" t="s">
         <v>126</v>
@@ -7253,21 +7256,24 @@
         <v>200</v>
       </c>
       <c r="R3" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+        <v>766</v>
+      </c>
+      <c r="S3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>467</v>
       </c>
       <c r="B4" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C4" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D4" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="E4" t="s">
         <v>126</v>
@@ -7309,21 +7315,24 @@
         <v>300</v>
       </c>
       <c r="R4" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+        <v>769</v>
+      </c>
+      <c r="S4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>469</v>
       </c>
       <c r="B5" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C5" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D5" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="E5" t="s">
         <v>126</v>
@@ -7365,21 +7374,24 @@
         <v>400</v>
       </c>
       <c r="R5" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+        <v>772</v>
+      </c>
+      <c r="S5">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>471</v>
       </c>
       <c r="B6" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C6" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D6" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="E6" t="s">
         <v>126</v>
@@ -7421,21 +7433,24 @@
         <v>500</v>
       </c>
       <c r="R6" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+        <v>775</v>
+      </c>
+      <c r="S6">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>473</v>
       </c>
       <c r="B7" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C7" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D7" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="E7" t="s">
         <v>126</v>
@@ -7477,21 +7492,24 @@
         <v>600</v>
       </c>
       <c r="R7" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+        <v>778</v>
+      </c>
+      <c r="S7">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>475</v>
       </c>
       <c r="B8" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C8" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D8" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="E8" t="s">
         <v>126</v>
@@ -7533,21 +7551,24 @@
         <v>700</v>
       </c>
       <c r="R8" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+        <v>781</v>
+      </c>
+      <c r="S8">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>477</v>
       </c>
       <c r="B9" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C9" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D9" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="E9" t="s">
         <v>135</v>
@@ -7589,21 +7610,24 @@
         <v>800</v>
       </c>
       <c r="R9" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+        <v>784</v>
+      </c>
+      <c r="S9">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>479</v>
       </c>
       <c r="B10" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C10" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D10" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="E10" t="s">
         <v>137</v>
@@ -7645,21 +7669,24 @@
         <v>900</v>
       </c>
       <c r="R10" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+        <v>787</v>
+      </c>
+      <c r="S10">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>481</v>
       </c>
       <c r="B11" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C11" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D11" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="E11" t="s">
         <v>103</v>
@@ -7701,7 +7728,10 @@
         <v>1000</v>
       </c>
       <c r="R11" t="s">
-        <v>788</v>
+        <v>790</v>
+      </c>
+      <c r="S11">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -7710,11 +7740,11 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>170</v>
       </c>
@@ -7725,25 +7755,25 @@
         <v>99</v>
       </c>
       <c r="D1" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="E1" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="F1" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="G1" t="s">
         <v>609</v>
       </c>
       <c r="H1" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="I1" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="J1" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="K1" t="s">
         <v>354</v>
@@ -7752,12 +7782,12 @@
         <v>300</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B2" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C2" t="s">
         <v>178</v>
@@ -7787,15 +7817,15 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>800</v>
+      </c>
+      <c r="B3" t="s">
         <v>798</v>
-      </c>
-      <c r="B3" t="s">
-        <v>796</v>
       </c>
       <c r="C3" t="s">
         <v>281</v>
@@ -7825,15 +7855,15 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B4" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C4" t="s">
         <v>282</v>
@@ -7863,15 +7893,15 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B5" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C5" t="s">
         <v>279</v>
@@ -7901,15 +7931,15 @@
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B6" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C6" t="s">
         <v>178</v>
@@ -7939,15 +7969,15 @@
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B7" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C7" t="s">
         <v>281</v>
@@ -7977,15 +8007,15 @@
         <v>1</v>
       </c>
       <c r="L7" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B8" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C8" t="s">
         <v>282</v>
@@ -8015,15 +8045,15 @@
         <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B9" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C9" t="s">
         <v>279</v>
@@ -8053,15 +8083,15 @@
         <v>1</v>
       </c>
       <c r="L9" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B10" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C10" t="s">
         <v>178</v>
@@ -8091,15 +8121,15 @@
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B11" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C11" t="s">
         <v>281</v>
@@ -8129,7 +8159,7 @@
         <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
   </sheetData>
@@ -8138,11 +8168,11 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>703</v>
       </c>
@@ -8153,10 +8183,10 @@
         <v>290</v>
       </c>
       <c r="D1" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>584</v>
       </c>
@@ -8170,7 +8200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>586</v>
       </c>
@@ -8184,7 +8214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>588</v>
       </c>
@@ -8198,7 +8228,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>590</v>
       </c>
@@ -8212,7 +8242,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>592</v>
       </c>
@@ -8226,7 +8256,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>594</v>
       </c>
@@ -8240,7 +8270,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>596</v>
       </c>
@@ -8254,7 +8284,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>598</v>
       </c>
@@ -8268,7 +8298,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>600</v>
       </c>
@@ -8282,7 +8312,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>602</v>
       </c>
@@ -8302,30 +8332,30 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B1" t="s">
         <v>134</v>
       </c>
       <c r="C1" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="D1" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="E1" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B2" t="s">
         <v>135</v>
@@ -8340,9 +8370,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B3" t="s">
         <v>137</v>
@@ -8357,9 +8387,9 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B4" t="s">
         <v>103</v>
@@ -8380,25 +8410,25 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B1" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C1" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="D1" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="E1" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="F1" t="s">
         <v>756</v>
@@ -8407,9 +8437,9 @@
         <v>354</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B2" t="s">
         <v>722</v>
@@ -8430,9 +8460,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B3" t="s">
         <v>725</v>
@@ -8453,9 +8483,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B4" t="s">
         <v>728</v>
@@ -8476,9 +8506,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B5" t="s">
         <v>731</v>
@@ -8499,9 +8529,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B6" t="s">
         <v>734</v>
@@ -8522,9 +8552,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B7" t="s">
         <v>737</v>
@@ -8545,9 +8575,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B8" t="s">
         <v>740</v>
@@ -8568,9 +8598,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B9" t="s">
         <v>743</v>
@@ -8591,9 +8621,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B10" t="s">
         <v>746</v>
@@ -8614,9 +8644,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B11" t="s">
         <v>749</v>
@@ -8643,24 +8673,24 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B1" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B2" t="s">
         <v>613</v>
@@ -8669,9 +8699,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B3" t="s">
         <v>616</v>
@@ -8680,9 +8710,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B4" t="s">
         <v>619</v>
@@ -8691,9 +8721,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B5" t="s">
         <v>622</v>
@@ -8702,9 +8732,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B6" t="s">
         <v>625</v>
@@ -8713,9 +8743,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B7" t="s">
         <v>628</v>
@@ -8724,9 +8754,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B8" t="s">
         <v>631</v>
@@ -8735,9 +8765,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B9" t="s">
         <v>634</v>
@@ -8746,9 +8776,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B10" t="s">
         <v>637</v>
@@ -8757,9 +8787,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B11" t="s">
         <v>640</v>
@@ -8774,22 +8804,22 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B1" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C1" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="D1" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="E1" t="s">
         <v>697</v>
@@ -8801,9 +8831,9 @@
         <v>354</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B2" t="s">
         <v>426</v>
@@ -8821,9 +8851,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B3" t="s">
         <v>432</v>
@@ -8841,9 +8871,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B4" t="s">
         <v>436</v>
@@ -8861,9 +8891,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B5" t="s">
         <v>440</v>
@@ -8881,9 +8911,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B6" t="s">
         <v>444</v>
@@ -8901,9 +8931,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B7" t="s">
         <v>447</v>
@@ -8921,9 +8951,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B8" t="s">
         <v>450</v>
@@ -8941,9 +8971,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B9" t="s">
         <v>453</v>
@@ -8961,9 +8991,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B10" t="s">
         <v>456</v>
@@ -8981,9 +9011,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B11" t="s">
         <v>459</v>
@@ -9007,24 +9037,24 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B1" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C1" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B2" t="s">
         <v>426</v>
@@ -9033,9 +9063,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B3" t="s">
         <v>432</v>
@@ -9044,9 +9074,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B4" t="s">
         <v>436</v>
@@ -9055,9 +9085,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B5" t="s">
         <v>440</v>
@@ -9066,9 +9096,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B6" t="s">
         <v>444</v>
@@ -9077,9 +9107,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B7" t="s">
         <v>447</v>
@@ -9088,9 +9118,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B8" t="s">
         <v>450</v>
@@ -9099,9 +9129,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B9" t="s">
         <v>453</v>
@@ -9110,9 +9140,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B10" t="s">
         <v>456</v>
@@ -9121,9 +9151,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B11" t="s">
         <v>459</v>
@@ -9138,27 +9168,27 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B1" t="s">
         <v>214</v>
       </c>
       <c r="C1" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="D1" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -9176,11 +9206,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D185"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>21</v>
       </c>
@@ -9194,7 +9224,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>92</v>
       </c>
@@ -9208,7 +9238,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>92</v>
       </c>
@@ -9222,7 +9252,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -9236,7 +9266,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>92</v>
       </c>
@@ -9250,7 +9280,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -9264,7 +9294,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -9278,7 +9308,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -9292,7 +9322,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -9306,7 +9336,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -9320,7 +9350,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -9334,7 +9364,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -9348,7 +9378,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -9362,7 +9392,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -9376,7 +9406,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -9390,7 +9420,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -9404,7 +9434,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -9418,7 +9448,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
@@ -9432,7 +9462,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -9446,7 +9476,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -9460,7 +9490,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -9474,7 +9504,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -9488,7 +9518,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -9502,7 +9532,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -9516,7 +9546,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -9530,7 +9560,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -9544,7 +9574,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -9558,7 +9588,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -9572,7 +9602,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -9586,7 +9616,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>129</v>
       </c>
@@ -9600,7 +9630,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>129</v>
       </c>
@@ -9614,7 +9644,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>129</v>
       </c>
@@ -9628,7 +9658,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>129</v>
       </c>
@@ -9642,7 +9672,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>66</v>
       </c>
@@ -9656,7 +9686,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>66</v>
       </c>
@@ -9670,7 +9700,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>66</v>
       </c>
@@ -9684,7 +9714,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>138</v>
       </c>
@@ -9698,7 +9728,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>138</v>
       </c>
@@ -9712,7 +9742,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>138</v>
       </c>
@@ -9726,7 +9756,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>138</v>
       </c>
@@ -9740,7 +9770,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>138</v>
       </c>
@@ -9754,7 +9784,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>138</v>
       </c>
@@ -9768,7 +9798,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>138</v>
       </c>
@@ -9782,7 +9812,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>138</v>
       </c>
@@ -9796,7 +9826,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>138</v>
       </c>
@@ -9810,7 +9840,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>138</v>
       </c>
@@ -9824,7 +9854,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>138</v>
       </c>
@@ -9838,7 +9868,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>138</v>
       </c>
@@ -9852,7 +9882,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>138</v>
       </c>
@@ -9866,7 +9896,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>138</v>
       </c>
@@ -9880,7 +9910,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>138</v>
       </c>
@@ -9894,7 +9924,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>138</v>
       </c>
@@ -9908,7 +9938,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>161</v>
       </c>
@@ -9922,7 +9952,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>161</v>
       </c>
@@ -9936,7 +9966,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>166</v>
       </c>
@@ -9950,7 +9980,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>166</v>
       </c>
@@ -9964,7 +9994,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>31</v>
       </c>
@@ -9978,7 +10008,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>31</v>
       </c>
@@ -9992,7 +10022,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>55</v>
       </c>
@@ -10006,7 +10036,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>55</v>
       </c>
@@ -10020,7 +10050,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>55</v>
       </c>
@@ -10034,7 +10064,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>55</v>
       </c>
@@ -10048,7 +10078,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>55</v>
       </c>
@@ -10062,7 +10092,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>55</v>
       </c>
@@ -10076,7 +10106,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>55</v>
       </c>
@@ -10090,7 +10120,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>55</v>
       </c>
@@ -10104,7 +10134,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>182</v>
       </c>
@@ -10118,7 +10148,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>182</v>
       </c>
@@ -10132,7 +10162,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>182</v>
       </c>
@@ -10146,7 +10176,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>182</v>
       </c>
@@ -10160,7 +10190,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>182</v>
       </c>
@@ -10174,7 +10204,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>182</v>
       </c>
@@ -10188,7 +10218,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>182</v>
       </c>
@@ -10202,7 +10232,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>182</v>
       </c>
@@ -10216,7 +10246,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>182</v>
       </c>
@@ -10230,7 +10260,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>182</v>
       </c>
@@ -10244,7 +10274,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>182</v>
       </c>
@@ -10258,7 +10288,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>182</v>
       </c>
@@ -10272,7 +10302,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>182</v>
       </c>
@@ -10286,7 +10316,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>182</v>
       </c>
@@ -10300,7 +10330,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>182</v>
       </c>
@@ -10314,7 +10344,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>182</v>
       </c>
@@ -10328,7 +10358,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>193</v>
       </c>
@@ -10342,7 +10372,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>193</v>
       </c>
@@ -10356,7 +10386,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>198</v>
       </c>
@@ -10370,7 +10400,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>198</v>
       </c>
@@ -10384,7 +10414,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>198</v>
       </c>
@@ -10398,7 +10428,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>198</v>
       </c>
@@ -10412,7 +10442,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>33</v>
       </c>
@@ -10426,7 +10456,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>33</v>
       </c>
@@ -10440,7 +10470,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>33</v>
       </c>
@@ -10454,7 +10484,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>33</v>
       </c>
@@ -10468,7 +10498,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>33</v>
       </c>
@@ -10482,7 +10512,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>33</v>
       </c>
@@ -10496,7 +10526,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>33</v>
       </c>
@@ -10510,7 +10540,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>33</v>
       </c>
@@ -10524,7 +10554,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>33</v>
       </c>
@@ -10538,7 +10568,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>33</v>
       </c>
@@ -10552,7 +10582,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>33</v>
       </c>
@@ -10566,7 +10596,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>33</v>
       </c>
@@ -10580,7 +10610,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>33</v>
       </c>
@@ -10594,7 +10624,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>33</v>
       </c>
@@ -10608,7 +10638,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>33</v>
       </c>
@@ -10622,7 +10652,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>33</v>
       </c>
@@ -10636,7 +10666,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>33</v>
       </c>
@@ -10650,7 +10680,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>33</v>
       </c>
@@ -10664,7 +10694,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>33</v>
       </c>
@@ -10678,7 +10708,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>33</v>
       </c>
@@ -10692,7 +10722,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>33</v>
       </c>
@@ -10706,7 +10736,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>33</v>
       </c>
@@ -10720,7 +10750,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>222</v>
       </c>
@@ -10734,7 +10764,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>222</v>
       </c>
@@ -10748,7 +10778,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>222</v>
       </c>
@@ -10762,7 +10792,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>222</v>
       </c>
@@ -10776,7 +10806,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>226</v>
       </c>
@@ -10790,7 +10820,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>226</v>
       </c>
@@ -10804,7 +10834,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>226</v>
       </c>
@@ -10818,7 +10848,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>226</v>
       </c>
@@ -10832,7 +10862,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>230</v>
       </c>
@@ -10846,7 +10876,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>230</v>
       </c>
@@ -10860,7 +10890,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>230</v>
       </c>
@@ -10874,7 +10904,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>57</v>
       </c>
@@ -10888,7 +10918,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>57</v>
       </c>
@@ -10902,7 +10932,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>57</v>
       </c>
@@ -10916,7 +10946,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>57</v>
       </c>
@@ -10930,7 +10960,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>57</v>
       </c>
@@ -10944,7 +10974,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>57</v>
       </c>
@@ -10958,7 +10988,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>57</v>
       </c>
@@ -10972,7 +11002,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>57</v>
       </c>
@@ -10986,7 +11016,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>242</v>
       </c>
@@ -11000,7 +11030,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>242</v>
       </c>
@@ -11014,7 +11044,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>242</v>
       </c>
@@ -11028,7 +11058,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>242</v>
       </c>
@@ -11042,7 +11072,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>242</v>
       </c>
@@ -11056,7 +11086,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>250</v>
       </c>
@@ -11070,7 +11100,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>250</v>
       </c>
@@ -11084,7 +11114,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>250</v>
       </c>
@@ -11098,7 +11128,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>250</v>
       </c>
@@ -11112,7 +11142,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>253</v>
       </c>
@@ -11126,7 +11156,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>253</v>
       </c>
@@ -11140,7 +11170,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>253</v>
       </c>
@@ -11154,7 +11184,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>253</v>
       </c>
@@ -11168,7 +11198,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>253</v>
       </c>
@@ -11182,7 +11212,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>253</v>
       </c>
@@ -11196,7 +11226,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>253</v>
       </c>
@@ -11210,7 +11240,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>253</v>
       </c>
@@ -11224,7 +11254,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>60</v>
       </c>
@@ -11238,7 +11268,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>60</v>
       </c>
@@ -11252,7 +11282,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>60</v>
       </c>
@@ -11266,7 +11296,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>60</v>
       </c>
@@ -11280,7 +11310,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>41</v>
       </c>
@@ -11294,7 +11324,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>41</v>
       </c>
@@ -11308,7 +11338,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>41</v>
       </c>
@@ -11322,7 +11352,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>41</v>
       </c>
@@ -11336,7 +11366,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>272</v>
       </c>
@@ -11350,7 +11380,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>272</v>
       </c>
@@ -11364,7 +11394,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>272</v>
       </c>
@@ -11378,7 +11408,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>272</v>
       </c>
@@ -11392,7 +11422,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>62</v>
       </c>
@@ -11406,7 +11436,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>62</v>
       </c>
@@ -11420,7 +11450,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>62</v>
       </c>
@@ -11434,7 +11464,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>62</v>
       </c>
@@ -11448,7 +11478,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>283</v>
       </c>
@@ -11462,7 +11492,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>283</v>
       </c>
@@ -11476,7 +11506,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>45</v>
       </c>
@@ -11490,7 +11520,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>45</v>
       </c>
@@ -11504,7 +11534,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>45</v>
       </c>
@@ -11518,7 +11548,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>64</v>
       </c>
@@ -11532,7 +11562,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>64</v>
       </c>
@@ -11546,7 +11576,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>64</v>
       </c>
@@ -11560,7 +11590,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>64</v>
       </c>
@@ -11574,7 +11604,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>64</v>
       </c>
@@ -11588,7 +11618,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>64</v>
       </c>
@@ -11602,7 +11632,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>64</v>
       </c>
@@ -11616,7 +11646,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>49</v>
       </c>
@@ -11630,7 +11660,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>49</v>
       </c>
@@ -11644,7 +11674,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>49</v>
       </c>
@@ -11658,7 +11688,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>49</v>
       </c>
@@ -11672,7 +11702,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>49</v>
       </c>
@@ -11686,7 +11716,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>49</v>
       </c>
@@ -11700,7 +11730,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>49</v>
       </c>
@@ -11714,7 +11744,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>49</v>
       </c>
@@ -11728,7 +11758,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>49</v>
       </c>
@@ -11742,7 +11772,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>49</v>
       </c>
@@ -11756,7 +11786,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>49</v>
       </c>
@@ -11776,93 +11806,93 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B1" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -11874,30 +11904,30 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B1" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C1" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="D1" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B2" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C2">
         <v>10</v>
@@ -11912,13 +11942,13 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B1" t="s">
         <v>214</v>
@@ -11927,9 +11957,9 @@
         <v>337</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -11944,11 +11974,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>300</v>
       </c>
@@ -11986,7 +12016,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>310</v>
       </c>
@@ -12024,7 +12054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>314</v>
       </c>
@@ -12062,7 +12092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>316</v>
       </c>
@@ -12100,7 +12130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>318</v>
       </c>
@@ -12138,7 +12168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>320</v>
       </c>
@@ -12176,7 +12206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>322</v>
       </c>
@@ -12214,7 +12244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>324</v>
       </c>
@@ -12252,7 +12282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>326</v>
       </c>
@@ -12290,7 +12320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>328</v>
       </c>
@@ -12328,7 +12358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>330</v>
       </c>
@@ -12372,11 +12402,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>113</v>
       </c>
@@ -12393,7 +12423,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>114</v>
       </c>
@@ -12410,7 +12440,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>116</v>
       </c>
@@ -12427,7 +12457,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>117</v>
       </c>
@@ -12444,7 +12474,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>118</v>
       </c>
@@ -12461,7 +12491,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>119</v>
       </c>
@@ -12478,7 +12508,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>120</v>
       </c>
@@ -12495,7 +12525,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>121</v>
       </c>
@@ -12512,7 +12542,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>122</v>
       </c>
@@ -12529,7 +12559,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>114</v>
       </c>
@@ -12546,7 +12576,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>116</v>
       </c>
@@ -12569,11 +12599,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>335</v>
       </c>
@@ -12593,7 +12623,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>340</v>
       </c>
@@ -12613,7 +12643,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>344</v>
       </c>
@@ -12633,7 +12663,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>345</v>
       </c>
@@ -12653,7 +12683,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>346</v>
       </c>
@@ -12673,7 +12703,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>347</v>
       </c>
@@ -12693,7 +12723,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>348</v>
       </c>
@@ -12713,7 +12743,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>349</v>
       </c>
@@ -12733,7 +12763,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>350</v>
       </c>
@@ -12753,7 +12783,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>351</v>
       </c>
@@ -12773,7 +12803,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>352</v>
       </c>
@@ -12799,11 +12829,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>170</v>
       </c>
@@ -12814,7 +12844,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>171</v>
       </c>
@@ -12825,7 +12855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>173</v>
       </c>
@@ -12842,11 +12872,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>170</v>
       </c>
@@ -12887,7 +12917,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>361</v>
       </c>
@@ -12925,7 +12955,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>366</v>
       </c>
@@ -12963,7 +12993,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>369</v>
       </c>
@@ -13001,7 +13031,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>372</v>
       </c>
@@ -13042,7 +13072,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>375</v>
       </c>
@@ -13083,7 +13113,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>378</v>
       </c>
@@ -13124,7 +13154,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>381</v>
       </c>
@@ -13165,7 +13195,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>384</v>
       </c>
@@ -13203,7 +13233,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>387</v>
       </c>
@@ -13241,7 +13271,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>390</v>
       </c>
@@ -13285,11 +13315,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>300</v>
       </c>
@@ -13300,7 +13330,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>395</v>
       </c>
@@ -13311,7 +13341,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>398</v>
       </c>
@@ -13322,7 +13352,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>400</v>
       </c>
@@ -13333,7 +13363,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>402</v>
       </c>
@@ -13344,7 +13374,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>404</v>
       </c>
@@ -13355,7 +13385,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>406</v>
       </c>
@@ -13366,7 +13396,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>408</v>
       </c>
@@ -13377,7 +13407,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>410</v>
       </c>
@@ -13388,7 +13418,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>412</v>
       </c>
@@ -13399,7 +13429,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>414</v>
       </c>
